--- a/Result/profitability/3067.xlsx
+++ b/Result/profitability/3067.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.12625</v>
+        <v>-0.09874999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>29.375</v>
+        <v>28.43375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>-0.08</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.10875</v>
+        <v>-0.05624999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>24.80625</v>
+        <v>26.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.61</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02000000000000002</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>26.185</v>
+        <v>27.065</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-2.46</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2975</v>
+        <v>-0.19375</v>
       </c>
       <c r="N5" t="n">
-        <v>19.6675</v>
+        <v>20.60625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.22875</v>
+        <v>-0.22125</v>
       </c>
       <c r="N6" t="n">
-        <v>18.1575</v>
+        <v>18.82</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2975</v>
+        <v>-0.295</v>
       </c>
       <c r="N7" t="n">
-        <v>15.52625</v>
+        <v>16.27375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.125</v>
+        <v>-0.14</v>
       </c>
       <c r="N8" t="n">
-        <v>15.91</v>
+        <v>16.46375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.51</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07624999999999998</v>
+        <v>-0.07624999999999996</v>
       </c>
       <c r="N9" t="n">
         <v>15.15625</v>
@@ -1645,7 +1645,7 @@
         <v>0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07375</v>
+        <v>-0.07374999999999995</v>
       </c>
       <c r="N10" t="n">
         <v>14.72875</v>
@@ -1772,7 +1772,7 @@
         <v>0.64</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01625</v>
+        <v>0.01625000000000004</v>
       </c>
       <c r="N11" t="n">
         <v>16.87625</v>
@@ -1899,7 +1899,7 @@
         <v>0.92</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05500000000000001</v>
+        <v>0.05500000000000005</v>
       </c>
       <c r="N12" t="n">
         <v>16.42375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3067</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-28.26%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.16875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.945</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1457236842105263</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.509999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2748901903367496</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
